--- a/data/trans_dic/P1416-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1416-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,48</t>
+          <t>5,02; 10,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,93</t>
+          <t>3,73; 7,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,63</t>
+          <t>3,94; 9,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 12,7</t>
+          <t>6,79; 12,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,1</t>
+          <t>6,98; 14,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,21</t>
+          <t>6,8; 13,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 13,75</t>
+          <t>7,0; 13,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,8; 18,84</t>
+          <t>13,19; 18,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,79</t>
+          <t>6,71; 10,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,57</t>
+          <t>5,52; 9,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,82</t>
+          <t>5,84; 10,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,3</t>
+          <t>10,35; 14,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 10,73</t>
+          <t>5,1; 10,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,26</t>
+          <t>3,36; 8,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,19</t>
+          <t>3,32; 8,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,27</t>
+          <t>6,96; 12,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 18,34</t>
+          <t>10,61; 18,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,06</t>
+          <t>7,7; 14,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 13,4</t>
+          <t>7,46; 13,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 16,33</t>
+          <t>10,72; 16,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 13,24</t>
+          <t>8,61; 13,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,29</t>
+          <t>6,06; 10,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,99</t>
+          <t>5,88; 10,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,8</t>
+          <t>9,3; 13,6</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,03</t>
+          <t>5,42; 10,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,19</t>
+          <t>3,93; 8,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,66</t>
+          <t>2,72; 6,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,96</t>
+          <t>8,88; 15,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,45</t>
+          <t>3,09; 10,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,13</t>
+          <t>4,87; 11,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,96</t>
+          <t>6,84; 16,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 18,69</t>
+          <t>10,08; 18,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,45</t>
+          <t>5,39; 9,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,08</t>
+          <t>4,78; 8,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,03</t>
+          <t>4,42; 8,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,7</t>
+          <t>10,4; 15,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,5</t>
+          <t>4,74; 7,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,96</t>
+          <t>3,51; 6,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,73</t>
+          <t>2,55; 4,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,96</t>
+          <t>6,25; 9,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,44</t>
+          <t>8,06; 12,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,08</t>
+          <t>6,62; 11,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,92</t>
+          <t>6,1; 10,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,26</t>
+          <t>10,2; 14,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,76</t>
+          <t>6,27; 8,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,48</t>
+          <t>5,18; 7,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,42</t>
+          <t>4,4; 6,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,33</t>
+          <t>8,37; 11,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,61</t>
+          <t>3,42; 8,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,23</t>
+          <t>2,29; 6,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,42</t>
+          <t>3,22; 6,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,07</t>
+          <t>7,34; 13,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 13,55</t>
+          <t>8,24; 13,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,41</t>
+          <t>3,25; 6,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 9,24</t>
+          <t>5,3; 9,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,63</t>
+          <t>9,76; 13,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,85</t>
+          <t>6,93; 10,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,69</t>
+          <t>3,12; 5,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,42</t>
+          <t>4,77; 7,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,0</t>
+          <t>9,35; 12,72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,02</t>
+          <t>5,12; 11,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,48</t>
+          <t>4,23; 11,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,49</t>
+          <t>6,84; 14,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 26,67</t>
+          <t>8,28; 23,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,42</t>
+          <t>6,53; 9,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,95</t>
+          <t>4,94; 8,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,6</t>
+          <t>5,25; 8,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,13</t>
+          <t>6,27; 9,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,37</t>
+          <t>6,49; 9,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,14</t>
+          <t>5,32; 8,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,91</t>
+          <t>6,09; 8,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,85</t>
+          <t>7,25; 11,6</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,59</t>
+          <t>5,84; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 5,9</t>
+          <t>4,37; 5,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,79</t>
+          <t>4,25; 5,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,08</t>
+          <t>8,7; 10,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,68</t>
+          <t>8,63; 10,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,26</t>
+          <t>6,4; 8,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,88</t>
+          <t>7,08; 8,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,57; 11,76</t>
+          <t>10,77; 12,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,88</t>
+          <t>7,48; 8,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,87</t>
+          <t>5,7; 6,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,1</t>
+          <t>5,93; 7,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 10,94</t>
+          <t>10,08; 11,55</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>76695</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>117170</t>
+          <t>128224</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24469; 49648</t>
+          <t>23766; 48360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15613; 34651</t>
+          <t>16304; 34240</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16536; 37011</t>
+          <t>16889; 38636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34933; 64047</t>
+          <t>37333; 69290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21626; 43248</t>
+          <t>21416; 43927</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22461; 44682</t>
+          <t>21389; 42524</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24405; 47725</t>
+          <t>24296; 46170</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57053; 83944</t>
+          <t>64175; 90652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50592; 84238</t>
+          <t>52353; 84553</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43268; 71901</t>
+          <t>41506; 71081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45808; 76244</t>
+          <t>45298; 77583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97939; 135794</t>
+          <t>107244; 150580</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46523</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>55821</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96574</t>
+          <t>102553</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18808; 39367</t>
+          <t>18708; 39819</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14140; 34578</t>
+          <t>14058; 34467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12801; 30905</t>
+          <t>12541; 31424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33775; 64384</t>
+          <t>33572; 62084</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39317; 68211</t>
+          <t>39455; 67186</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27127; 50919</t>
+          <t>26020; 50307</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26867; 49894</t>
+          <t>27755; 51379</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39354; 62253</t>
+          <t>45184; 69555</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64549; 97805</t>
+          <t>63642; 97863</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45038; 77882</t>
+          <t>45827; 77280</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43755; 74869</t>
+          <t>44049; 75251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78360; 114916</t>
+          <t>84037; 122898</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73572</t>
+          <t>82835</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28946; 54392</t>
+          <t>29372; 54597</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24633; 51459</t>
+          <t>24671; 51314</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15053; 34737</t>
+          <t>14221; 33583</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19345; 86407</t>
+          <t>41696; 71653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5072; 17532</t>
+          <t>5179; 18386</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11829; 28942</t>
+          <t>12668; 29620</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11627; 28176</t>
+          <t>11360; 27727</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16717; 31142</t>
+          <t>18878; 34179</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37985; 67088</t>
+          <t>38275; 66756</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41556; 71801</t>
+          <t>42480; 75382</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31206; 55221</t>
+          <t>30431; 56302</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29602; 114153</t>
+          <t>68310; 100878</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82271</t>
+          <t>90258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90196</t>
+          <t>103605</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>172467</t>
+          <t>193863</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58363; 92905</t>
+          <t>58740; 91953</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39314; 69035</t>
+          <t>40701; 69854</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29735; 54399</t>
+          <t>29358; 53747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64190; 103017</t>
+          <t>70759; 111275</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57255; 88864</t>
+          <t>57573; 88281</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50954; 84923</t>
+          <t>50785; 85670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50892; 81939</t>
+          <t>50359; 83131</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45754; 119331</t>
+          <t>87299; 121424</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124331; 171013</t>
+          <t>122485; 169248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98919; 143947</t>
+          <t>99731; 143253</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87599; 126841</t>
+          <t>86980; 128007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>122475; 207501</t>
+          <t>166404; 221745</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>56570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>133481</t>
+          <t>151719</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12783; 30166</t>
+          <t>12004; 28779</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12916; 31809</t>
+          <t>11714; 31024</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18848; 39872</t>
+          <t>19965; 42590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38645; 71438</t>
+          <t>41595; 74689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45634; 77060</t>
+          <t>46887; 75730</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24401; 48767</t>
+          <t>24720; 48407</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39204; 68184</t>
+          <t>39125; 67125</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59277; 97279</t>
+          <t>80737; 111331</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64406; 99788</t>
+          <t>63686; 98972</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41636; 72369</t>
+          <t>39713; 69239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63534; 100886</t>
+          <t>64805; 100917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105619; 157216</t>
+          <t>130287; 177349</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>33346</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61672</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>100566</t>
+          <t>100009</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14316; 32847</t>
+          <t>15270; 33330</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12555; 30635</t>
+          <t>11298; 29383</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20308; 41602</t>
+          <t>19629; 41039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20984; 63921</t>
+          <t>19572; 54931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>80370; 117687</t>
+          <t>81541; 118681</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56641; 88212</t>
+          <t>54802; 89839</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57211; 93012</t>
+          <t>56827; 90926</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50143; 76681</t>
+          <t>52625; 82038</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102326; 144919</t>
+          <t>100401; 140870</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73554; 112079</t>
+          <t>73267; 110946</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82077; 121937</t>
+          <t>83397; 122736</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>77511; 128139</t>
+          <t>78002; 124895</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318736</t>
+          <t>335271</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>375094</t>
+          <t>423932</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>693829</t>
+          <t>759202</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>190978; 248115</t>
+          <t>191040; 248433</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>150909; 201957</t>
+          <t>149342; 203834</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>144293; 196060</t>
+          <t>143948; 193786</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>247471; 373494</t>
+          <t>298825; 375799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>291470; 360902</t>
+          <t>291623; 361410</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>229479; 292990</t>
+          <t>227139; 291113</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>247835; 313438</t>
+          <t>250141; 315692</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>305202; 418763</t>
+          <t>389631; 458027</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>500184; 590696</t>
+          <t>497399; 595713</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>392733; 478782</t>
+          <t>397514; 477824</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>410801; 490926</t>
+          <t>410250; 491708</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>597327; 757948</t>
+          <t>710899; 815158</t>
         </is>
       </c>
     </row>
